--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.51661559975632</v>
+        <v>7.396450034960402</v>
       </c>
       <c r="D2" t="n">
-        <v>45.26156504510757</v>
+        <v>7.355004319829981</v>
       </c>
       <c r="E2" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F2" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.19224752286948</v>
+        <v>7.34374022246629</v>
       </c>
       <c r="D3" t="n">
-        <v>45.0328390630379</v>
+        <v>7.317836347743659</v>
       </c>
       <c r="E3" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F3" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.9796097720774</v>
+        <v>5.521686587962577</v>
       </c>
       <c r="D4" t="n">
-        <v>33.51063981313378</v>
+        <v>5.445478969634239</v>
       </c>
       <c r="E4" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F4" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.33075056759372</v>
+        <v>3.303746967233979</v>
       </c>
       <c r="D5" t="n">
-        <v>19.87961059101806</v>
+        <v>3.230436721040435</v>
       </c>
       <c r="E5" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F5" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.72434980495647</v>
+        <v>7.430206843305426</v>
       </c>
       <c r="D6" t="n">
-        <v>46.15910984008161</v>
+        <v>7.500855349013262</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F6" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.413878703692081</v>
+        <v>1.367255289349963</v>
       </c>
       <c r="D7" t="n">
-        <v>8.763601575987638</v>
+        <v>1.424085256097991</v>
       </c>
       <c r="E7" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F7" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.00738127693171</v>
+        <v>6.988699457501403</v>
       </c>
       <c r="D8" t="n">
-        <v>42.62250686698965</v>
+        <v>6.926157365885818</v>
       </c>
       <c r="E8" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F8" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.70126355441695</v>
+        <v>8.076455327592754</v>
       </c>
       <c r="D9" t="n">
-        <v>49.60013712750594</v>
+        <v>8.060022283219716</v>
       </c>
       <c r="E9" t="n">
-        <v>13.76221042399414</v>
+        <v>2.236359193899048</v>
       </c>
       <c r="F9" t="n">
-        <v>13.72170614794728</v>
+        <v>2.229777249041433</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
